--- a/data/gravel/Niner Ore 9 RDO 2025.xlsx
+++ b/data/gravel/Niner Ore 9 RDO 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8016778D-35F7-934B-A967-18B2569EDCC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E57E48E2-8FCD-7D48-9EB5-82F24AE18C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="13120" windowHeight="6100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33920" yWindow="-17100" windowWidth="22440" windowHeight="12880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -100,9 +100,6 @@
     <t>(C) CHAINSTAY LENGTH ACTUAL</t>
   </si>
   <si>
-    <t>rear_center</t>
-  </si>
-  <si>
     <t>(D) HORIZONTAL CHAINSTAY</t>
   </si>
   <si>
@@ -367,9 +364,6 @@
     <t>currency</t>
   </si>
   <si>
-    <t>us</t>
-  </si>
-  <si>
     <t>class</t>
   </si>
   <si>
@@ -386,17 +380,29 @@
   </si>
   <si>
     <t>rigid</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>rear_center_h</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Futura"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Futura"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -419,8 +425,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -876,11 +883,11 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B12" t="s">
         <v>26</v>
-      </c>
-      <c r="B12" t="s">
-        <v>27</v>
       </c>
       <c r="C12">
         <v>430</v>
@@ -903,10 +910,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" t="s">
         <v>28</v>
-      </c>
-      <c r="B13" t="s">
-        <v>29</v>
       </c>
       <c r="C13">
         <v>609</v>
@@ -929,10 +936,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s">
         <v>30</v>
-      </c>
-      <c r="B14" t="s">
-        <v>31</v>
       </c>
       <c r="C14">
         <v>1034</v>
@@ -955,10 +962,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" t="s">
         <v>32</v>
-      </c>
-      <c r="B15" t="s">
-        <v>33</v>
       </c>
       <c r="C15">
         <v>70</v>
@@ -981,10 +988,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s">
         <v>34</v>
-      </c>
-      <c r="B16" t="s">
-        <v>35</v>
       </c>
       <c r="C16">
         <v>90</v>
@@ -1007,10 +1014,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" t="s">
         <v>36</v>
-      </c>
-      <c r="B17" t="s">
-        <v>37</v>
       </c>
       <c r="C17">
         <v>69</v>
@@ -1033,10 +1040,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" t="s">
         <v>38</v>
-      </c>
-      <c r="B18" t="s">
-        <v>39</v>
       </c>
       <c r="C18">
         <v>74</v>
@@ -1059,10 +1066,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" t="s">
         <v>40</v>
-      </c>
-      <c r="B19" t="s">
-        <v>41</v>
       </c>
       <c r="C19">
         <v>693</v>
@@ -1085,10 +1092,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" t="s">
         <v>42</v>
-      </c>
-      <c r="B20" t="s">
-        <v>43</v>
       </c>
       <c r="C20">
         <v>369</v>
@@ -1111,10 +1118,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" t="s">
         <v>44</v>
-      </c>
-      <c r="B21" t="s">
-        <v>45</v>
       </c>
       <c r="C21">
         <v>545</v>
@@ -1137,10 +1144,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" t="s">
         <v>46</v>
-      </c>
-      <c r="B22" t="s">
-        <v>47</v>
       </c>
       <c r="C22">
         <v>50</v>
@@ -1163,17 +1170,17 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C25">
         <v>440</v>
@@ -1196,7 +1203,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C26">
         <v>170</v>
@@ -1219,7 +1226,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C27">
         <v>420</v>
@@ -1242,7 +1249,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C28">
         <v>50</v>
@@ -1265,7 +1272,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C29">
         <v>700</v>
@@ -1288,7 +1295,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C30">
         <v>40</v>
@@ -1311,7 +1318,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C31">
         <v>50</v>
@@ -1334,7 +1341,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C32">
         <v>150</v>
@@ -1357,7 +1364,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C33">
         <v>158.5</v>
@@ -1380,305 +1387,305 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>58</v>
+      </c>
+      <c r="B35" t="s">
         <v>59</v>
-      </c>
-      <c r="B35" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B36" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B37" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B38" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" t="s">
         <v>61</v>
-      </c>
-      <c r="B39" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>62</v>
+      </c>
+      <c r="B40" t="s">
         <v>63</v>
-      </c>
-      <c r="B40" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>64</v>
+      </c>
+      <c r="B41" t="s">
         <v>65</v>
-      </c>
-      <c r="B41" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>66</v>
+      </c>
+      <c r="B42" t="s">
         <v>67</v>
-      </c>
-      <c r="B42" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>68</v>
+      </c>
+      <c r="B43" t="s">
         <v>69</v>
-      </c>
-      <c r="B43" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>70</v>
+      </c>
+      <c r="B44" t="s">
         <v>71</v>
-      </c>
-      <c r="B44" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>72</v>
+      </c>
+      <c r="B45" t="s">
         <v>73</v>
-      </c>
-      <c r="B45" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B46" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B47" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>76</v>
+      </c>
+      <c r="B48" t="s">
         <v>77</v>
-      </c>
-      <c r="B48" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>78</v>
+      </c>
+      <c r="B49" t="s">
         <v>79</v>
-      </c>
-      <c r="B49" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>80</v>
+      </c>
+      <c r="B50" t="s">
         <v>81</v>
-      </c>
-      <c r="B50" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>82</v>
+      </c>
+      <c r="B51" t="s">
         <v>83</v>
-      </c>
-      <c r="B51" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>84</v>
+      </c>
+      <c r="B52" t="s">
         <v>85</v>
-      </c>
-      <c r="B52" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B53" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>87</v>
+      </c>
+      <c r="B54" t="s">
         <v>88</v>
-      </c>
-      <c r="B54" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>89</v>
+      </c>
+      <c r="B55" t="s">
         <v>90</v>
-      </c>
-      <c r="B55" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
+        <v>91</v>
+      </c>
+      <c r="B56" t="s">
         <v>92</v>
-      </c>
-      <c r="B56" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B57" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B58" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
+        <v>95</v>
+      </c>
+      <c r="B59" t="s">
         <v>96</v>
-      </c>
-      <c r="B59" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B60" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B62" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B63" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
+        <v>101</v>
+      </c>
+      <c r="B64" t="s">
         <v>102</v>
-      </c>
-      <c r="B64" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B65" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B67" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B69" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>108</v>
+      </c>
+      <c r="B70" t="s">
         <v>109</v>
-      </c>
-      <c r="B70" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>110</v>
+      </c>
+      <c r="B71" t="s">
         <v>111</v>
-      </c>
-      <c r="B71" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>114</v>
-      </c>
-      <c r="B73" t="s">
-        <v>115</v>
+        <v>113</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Niner Ore 9 RDO 2025.xlsx
+++ b/data/gravel/Niner Ore 9 RDO 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E57E48E2-8FCD-7D48-9EB5-82F24AE18C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{404371AF-4BD9-AF45-ADD7-C65F3FE56425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33920" yWindow="-17100" windowWidth="22440" windowHeight="12880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="122">
   <si>
     <t>brand</t>
   </si>
@@ -1469,24 +1469,15 @@
       <c r="A45" t="s">
         <v>72</v>
       </c>
-      <c r="B45" t="s">
-        <v>73</v>
-      </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>74</v>
       </c>
-      <c r="B46" t="s">
-        <v>73</v>
-      </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>75</v>
-      </c>
-      <c r="B47" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">

--- a/data/gravel/Niner Ore 9 RDO 2025.xlsx
+++ b/data/gravel/Niner Ore 9 RDO 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{404371AF-4BD9-AF45-ADD7-C65F3FE56425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7E0C05B-96BF-164E-B767-9AB015A35BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="123">
   <si>
     <t>brand</t>
   </si>
@@ -46,9 +46,6 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://www.ninerbikes.com/ore-9-rdo-frameset/</t>
-  </si>
-  <si>
     <t>16-Jul-2025</t>
   </si>
   <si>
@@ -386,6 +383,12 @@
   </si>
   <si>
     <t>rear_center_h</t>
+  </si>
+  <si>
+    <t>https://www.ninerbikes.com/gravel/ore-9-rdo/</t>
+  </si>
+  <si>
+    <t>https://www.ninerbikes.com/media/catalog/product/cache/ba8ebf6c1416ca2f4a798d430e7c0a02/o/r/ore_9_rdo_-_4s_-_grx_1x.jpg</t>
   </si>
 </sst>
 </file>
@@ -759,7 +762,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -767,49 +770,54 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
         <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>14</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>15</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>16</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>17</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>18</v>
-      </c>
-      <c r="H8" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
         <v>20</v>
-      </c>
-      <c r="B9" t="s">
-        <v>21</v>
       </c>
       <c r="C9">
         <v>525</v>
@@ -832,10 +840,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
         <v>22</v>
-      </c>
-      <c r="B10" t="s">
-        <v>23</v>
       </c>
       <c r="C10">
         <v>430</v>
@@ -858,10 +866,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
         <v>24</v>
-      </c>
-      <c r="B11" t="s">
-        <v>25</v>
       </c>
       <c r="C11">
         <v>435</v>
@@ -884,10 +892,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12">
         <v>430</v>
@@ -910,10 +918,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" t="s">
         <v>27</v>
-      </c>
-      <c r="B13" t="s">
-        <v>28</v>
       </c>
       <c r="C13">
         <v>609</v>
@@ -936,10 +944,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
         <v>29</v>
-      </c>
-      <c r="B14" t="s">
-        <v>30</v>
       </c>
       <c r="C14">
         <v>1034</v>
@@ -962,10 +970,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s">
         <v>31</v>
-      </c>
-      <c r="B15" t="s">
-        <v>32</v>
       </c>
       <c r="C15">
         <v>70</v>
@@ -988,10 +996,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" t="s">
         <v>33</v>
-      </c>
-      <c r="B16" t="s">
-        <v>34</v>
       </c>
       <c r="C16">
         <v>90</v>
@@ -1014,10 +1022,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s">
         <v>35</v>
-      </c>
-      <c r="B17" t="s">
-        <v>36</v>
       </c>
       <c r="C17">
         <v>69</v>
@@ -1040,10 +1048,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" t="s">
         <v>37</v>
-      </c>
-      <c r="B18" t="s">
-        <v>38</v>
       </c>
       <c r="C18">
         <v>74</v>
@@ -1066,10 +1074,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" t="s">
         <v>39</v>
-      </c>
-      <c r="B19" t="s">
-        <v>40</v>
       </c>
       <c r="C19">
         <v>693</v>
@@ -1092,10 +1100,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" t="s">
         <v>41</v>
-      </c>
-      <c r="B20" t="s">
-        <v>42</v>
       </c>
       <c r="C20">
         <v>369</v>
@@ -1118,10 +1126,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" t="s">
         <v>43</v>
-      </c>
-      <c r="B21" t="s">
-        <v>44</v>
       </c>
       <c r="C21">
         <v>545</v>
@@ -1144,10 +1152,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" t="s">
         <v>45</v>
-      </c>
-      <c r="B22" t="s">
-        <v>46</v>
       </c>
       <c r="C22">
         <v>50</v>
@@ -1170,17 +1178,17 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C25">
         <v>440</v>
@@ -1203,7 +1211,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C26">
         <v>170</v>
@@ -1226,7 +1234,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C27">
         <v>420</v>
@@ -1249,7 +1257,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C28">
         <v>50</v>
@@ -1272,7 +1280,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C29">
         <v>700</v>
@@ -1295,7 +1303,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C30">
         <v>40</v>
@@ -1318,7 +1326,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C31">
         <v>50</v>
@@ -1341,7 +1349,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C32">
         <v>150</v>
@@ -1364,7 +1372,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C33">
         <v>158.5</v>
@@ -1387,296 +1395,296 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>57</v>
+      </c>
+      <c r="B35" t="s">
         <v>58</v>
-      </c>
-      <c r="B35" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>113</v>
+      </c>
+      <c r="B36" t="s">
         <v>114</v>
-      </c>
-      <c r="B36" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>115</v>
+      </c>
+      <c r="B37" t="s">
         <v>116</v>
-      </c>
-      <c r="B37" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>117</v>
+      </c>
+      <c r="B38" t="s">
         <v>118</v>
-      </c>
-      <c r="B38" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>59</v>
+      </c>
+      <c r="B39" t="s">
         <v>60</v>
-      </c>
-      <c r="B39" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40" t="s">
         <v>62</v>
-      </c>
-      <c r="B40" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>63</v>
+      </c>
+      <c r="B41" t="s">
         <v>64</v>
-      </c>
-      <c r="B41" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>65</v>
+      </c>
+      <c r="B42" t="s">
         <v>66</v>
-      </c>
-      <c r="B42" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>67</v>
+      </c>
+      <c r="B43" t="s">
         <v>68</v>
-      </c>
-      <c r="B43" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>69</v>
+      </c>
+      <c r="B44" t="s">
         <v>70</v>
-      </c>
-      <c r="B44" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>75</v>
+      </c>
+      <c r="B48" t="s">
         <v>76</v>
-      </c>
-      <c r="B48" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>77</v>
+      </c>
+      <c r="B49" t="s">
         <v>78</v>
-      </c>
-      <c r="B49" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>79</v>
+      </c>
+      <c r="B50" t="s">
         <v>80</v>
-      </c>
-      <c r="B50" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>81</v>
+      </c>
+      <c r="B51" t="s">
         <v>82</v>
-      </c>
-      <c r="B51" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>83</v>
+      </c>
+      <c r="B52" t="s">
         <v>84</v>
-      </c>
-      <c r="B52" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B53" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>86</v>
+      </c>
+      <c r="B54" t="s">
         <v>87</v>
-      </c>
-      <c r="B54" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>88</v>
+      </c>
+      <c r="B55" t="s">
         <v>89</v>
-      </c>
-      <c r="B55" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
+        <v>90</v>
+      </c>
+      <c r="B56" t="s">
         <v>91</v>
-      </c>
-      <c r="B56" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B57" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B58" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
+        <v>94</v>
+      </c>
+      <c r="B59" t="s">
         <v>95</v>
-      </c>
-      <c r="B59" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B60" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B62" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B63" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
+        <v>100</v>
+      </c>
+      <c r="B64" t="s">
         <v>101</v>
-      </c>
-      <c r="B64" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B65" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B66" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B67" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B69" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>107</v>
+      </c>
+      <c r="B70" t="s">
         <v>108</v>
-      </c>
-      <c r="B70" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>109</v>
+      </c>
+      <c r="B71" t="s">
         <v>110</v>
-      </c>
-      <c r="B71" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Niner Ore 9 RDO 2025.xlsx
+++ b/data/gravel/Niner Ore 9 RDO 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7E0C05B-96BF-164E-B767-9AB015A35BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D280DA2F-9C15-C043-819E-F040BEE9C68A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7460" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="125">
   <si>
     <t>brand</t>
   </si>
@@ -389,6 +389,12 @@
   </si>
   <si>
     <t>https://www.ninerbikes.com/media/catalog/product/cache/ba8ebf6c1416ca2f4a798d430e7c0a02/o/r/ore_9_rdo_-_4s_-_grx_1x.jpg</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Fort Collins, Colorado, USA</t>
   </si>
 </sst>
 </file>
@@ -727,7 +733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1687,6 +1693,14 @@
         <v>119</v>
       </c>
     </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>123</v>
+      </c>
+      <c r="B74" t="s">
+        <v>124</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Niner Ore 9 RDO 2025.xlsx
+++ b/data/gravel/Niner Ore 9 RDO 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D280DA2F-9C15-C043-819E-F040BEE9C68A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE5A5785-3F9B-B94C-8394-24C463415C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7460" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="131">
   <si>
     <t>brand</t>
   </si>
@@ -395,6 +395,24 @@
   </si>
   <si>
     <t>Fort Collins, Colorado, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -733,7 +751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1512,192 +1530,222 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>79</v>
-      </c>
-      <c r="B50" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>81</v>
-      </c>
-      <c r="B51" t="s">
-        <v>82</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>83</v>
-      </c>
-      <c r="B52" t="s">
-        <v>84</v>
+        <v>127</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>85</v>
-      </c>
-      <c r="B53" t="s">
-        <v>62</v>
+        <v>128</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>86</v>
-      </c>
-      <c r="B54" t="s">
-        <v>87</v>
+        <v>129</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>88</v>
-      </c>
-      <c r="B55" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="B56" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B57" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="B59" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B60" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>97</v>
+        <v>88</v>
+      </c>
+      <c r="B61" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B62" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B63" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B64" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B65" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B66" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>104</v>
-      </c>
-      <c r="B67" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>105</v>
+        <v>98</v>
+      </c>
+      <c r="B68" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="B69" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B70" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="B71" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>111</v>
+        <v>103</v>
+      </c>
+      <c r="B72" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>112</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>119</v>
+        <v>104</v>
+      </c>
+      <c r="B73" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>106</v>
+      </c>
+      <c r="B75" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>107</v>
+      </c>
+      <c r="B76" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>109</v>
+      </c>
+      <c r="B77" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>112</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>123</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B80" t="s">
         <v>124</v>
       </c>
     </row>

--- a/data/gravel/Niner Ore 9 RDO 2025.xlsx
+++ b/data/gravel/Niner Ore 9 RDO 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE5A5785-3F9B-B94C-8394-24C463415C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F2B7C7E-1357-9441-A432-B12E50E5D25B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="131">
   <si>
     <t>brand</t>
   </si>
@@ -1687,17 +1687,11 @@
       <c r="A72" t="s">
         <v>103</v>
       </c>
-      <c r="B72" t="s">
-        <v>64</v>
-      </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>104</v>
       </c>
-      <c r="B73" t="s">
-        <v>64</v>
-      </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
@@ -1707,9 +1701,6 @@
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>106</v>
-      </c>
-      <c r="B75" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
